--- a/design-campaign-EGFP/shortlists/shortlist_EBFP_MSA-gibbs.xlsx
+++ b/design-campaign-EGFP/shortlists/shortlist_EBFP_MSA-gibbs.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="shortlist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'shortlist'!$A$1:$O$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -425,8 +427,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -471,30 +490,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>n_mut_vs_EGFP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>is_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_bright</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>bright_logit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>aa_sequence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dna_sequence</t>
         </is>
@@ -521,16 +545,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKLTLKFICTTGKLPVPWPTLVTTLTYGVQCFSRYPDHMKQHDFFKSAMPEGYVQERTIFFKDDGNYKTRAEVKFEGDTLVNRIELKGIDFKEDGNILGHKLEYNYNSHNVYIMADKQKNGIKVNFKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQSALSKDPNEKRDHMVLLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACTGACCCTGAAATTTATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGGTGACCACCCTGACCTATGGCGTGCAGTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAGTGAAATTTGAAGGCGATACCCTGGTGAACCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACTATAACAGCCATAACGTGTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACTTTAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGAGCGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -557,16 +584,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKLTLKFICTTGKLPVPWPTLVTTLTHGVQCFSRYPDHMKQHDFFKSAMPEGYVQERTIFFKDDGNYKTRAEVKFEGDTLVNRIELKGIDFKEDGNILGHKLEYNFNSHNVYIMADKQKNGIKVNFKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQSALSKDPNEKRDHMVLLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACTGACCCTGAAATTTATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGGTGACCACCCTGACCCATGGCGTGCAGTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAGTGAAATTTGAAGGCGATACCCTGGTGAACCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACTTTAACAGCCATAACGTGTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACTTTAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGAGCGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -601,30 +631,33 @@
       <c r="H4" t="n">
         <v>461.4</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>-13.26</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKLTIKLICTTGKLPVPWPTLMHTLLHGVRCFSRYPDHMKQHDFFKSAMPEGYVQERTIFFKDDGNYKTRAEVKFEGDTLVNRIELKGIDFKEDGNILGHKLEYNEPSTNNYIMADKQKNGIKVNFKMRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQLALSKDPNEKRDHMVLLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACTGACCATTAAACTGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGATGCATACCCTGCTGCATGGCGTGCGCTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAGTGAAATTTGAAGGCGATACCCTGGTGAACCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGAACCGAGCACCAACAACTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACTTTAAAATGCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGCTGGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -659,30 +692,33 @@
       <c r="H5" t="n">
         <v>476.1</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I5" t="n">
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>-9.57</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKMTTKMICTTGKLPVPWPTLMAQLQHGNHCFSRYPDHMKQHDFFKSAMPEGYVQERTIFFKDDGNYKTRAEIKFEGDTLVYRIELKGIDFKEDGNILGHKLEYNYGSSNRYIMADKQKNGIKVNAKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSEQSALSKDPNEKRDHMVLLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAAATGACCACCAAAATGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGATGGCGCAGCTGCAGCATGGCAACCATTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAATTAAATTTGAAGGCGATACCCTGGTGTATCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACTATGGCAGCAGCAACCGCTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGCGAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCGAACAGAGCGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -717,30 +753,33 @@
       <c r="H6" t="n">
         <v>477.3</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I6" t="n">
+        <v>20</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>-12.34</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKYTAKLICTTGKLPVPWPTLSKTLGHGNPCFSRYPDHMKQHDFFKSAMPEGFVWERTIFFKDDGNYKTRAEIKFEGDTLVCRIELKGIDFKEDGNILGHKLEYNEPSTNVYIMADKQKNGIKVNVKQRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQIALSKDPNEKRDHMVVLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAATATACCGCGAAACTGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGAGCAAAACCCTGGGCCATGGCAACCCGTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTTTGTGTGGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAATTAAATTTGAAGGCGATACCCTGGTGTGCCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGAACCGAGCACCAACGTGTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGTGAAACAGCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGATTGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGGTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -775,30 +814,33 @@
       <c r="H7" t="n">
         <v>474.2</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I7" t="n">
+        <v>19</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>-13.9</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKQTMKLICTTGKLPVPWPTLVPTFQHGVRCFSRYPDHMKQHDFFKSAMPEGFVQERTIFFKDDGNYKTRAEIKFEGDTLVNRIELKGIDFKEDGNILGHKLEYNEPSTNRYIMADKQKNGIKVNVKMRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSHQTALSKDPNEKRDHMVVLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACAGACCATGAAACTGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGGTGCCGACCTTTCAGCATGGCGTGCGCTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTTTGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAATTAAATTTGAAGGCGATACCCTGGTGAACCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGAACCGAGCACCAACCGCTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGTGAAAATGCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCCATCAGACCGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGGTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -833,30 +875,33 @@
       <c r="H8" t="n">
         <v>484.1</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I8" t="n">
+        <v>16</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>-14.16</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKQTVKMICTTGKLPVPWPTLMTVISYGNRCFSRYPDHMKQHDFFKSAMPEGYVQERTIFFKDDGNYKTRAEIKFEGDTLVGRIELKGIDFKEDGNILGHKLEYNEPSHNHYIMADKQKNGIKVNDKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQIALSKDPNEKRDHMVLLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACAGACCGTGAAAATGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGATGACCGTGATTAGCTATGGCAACCGCTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAATTAAATTTGAAGGCGATACCCTGGTGGGCCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGAACCGAGCCATAACCATTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGATAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGATTGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -891,30 +936,33 @@
       <c r="H9" t="n">
         <v>482.3</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I9" t="n">
+        <v>18</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>-12.77</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKLTAKLICTTGKLPVPWPTLTTSISYGNKCFSRYPDHMKQHDFFKSAMPEGFVWERTIFFKDDGNYKTRAEVKFEGDTLVYRIELKGIDFKEDGNILGHKLEYNLPSTNIYIMADKQKNGIKVNVKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQNALSKDPNEKRDHMVQLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACTGACCGCGAAACTGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGACCACCAGCATTAGCTATGGCAACAAATGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTTTGTGTGGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAGTGAAATTTGAAGGCGATACCCTGGTGTATCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACCTGCCGAGCACCAACATTTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGTGAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGAACGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCAGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -949,30 +997,33 @@
       <c r="H10" t="n">
         <v>488.4</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I10" t="n">
+        <v>18</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>-9.98</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKQTMKAICTTGKLPVPWPTLSTSFSYGVRCFSRYPDHMKQHDFFKSAMPEGMVTERTIFFKDDGNYKTRAEVKFEGDTLVHRIELKGIDFKEDGNILGHKLEYNEKSHNRYIMADKQKNGIKVNSKWRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQLALSKDPNEKRDHMVQLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACAGACCATGAAAGCGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGAGCACCAGCTTTAGCTATGGCGTGCGCTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCATGGTGACCGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAGTGAAATTTGAAGGCGATACCCTGGTGCATCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGAAAAAAGCCATAACCGCTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACAGCAAATGGCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGCTGGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCAGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -1007,30 +1058,33 @@
       <c r="H11" t="n">
         <v>481.6</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I11" t="n">
+        <v>18</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>-10.64</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKITAKFICTTGKLPVPWPTMCTTISYGNKCFSRYPDHMKQHDFFKSAMPEGFVQERTIFFKDDGNYKTRAETKFEGDTLVHRIELKGIDFKEDGNILGHKLEYNYASSNHYIMADKQKNGIKVNDKMRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSTQLALSKDPNEKRDHMVQLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAAATTACCGCGAAATTTATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCATGTGCACCACCATTAGCTATGGCAACAAATGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTTTGTGCAGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAACCAAATTTGAAGGCGATACCCTGGTGCATCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACTATGCGAGCAGCAACCATTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGATAAAATGCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCACCCAGCTGGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGCAGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -1065,30 +1119,33 @@
       <c r="H12" t="n">
         <v>487.3</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I12" t="n">
+        <v>22</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>-17.39</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKQTAKLICTTGKLPVPWPTLTSVFSYGSQCFSRYPDHMKQHDFFKSAMPEGFVNERTIFFKDDGNYKTRAEYKFEGDTLVYRIELKGIDFKEDGNILGHKLEYNDASTNIYIMADKQKNGIKVNCKKRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSHQIALSKDPNEKRDHMVFLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAACAGACCGCGAAACTGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGACCAGCGTGTTTAGCTATGGCAGCCAGTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTTTGTGAACGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAATATAAATTTGAAGGCGATACCCTGGTGTATCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACGATGCGAGCACCAACATTTATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACTGCAAAAAACGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCCATCAGATTGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGTTTCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
@@ -1123,36 +1180,40 @@
       <c r="H13" t="n">
         <v>485.2</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I13" t="n">
+        <v>20</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>-10.92</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>designs</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>MVSKGEELFTGVVPILVELDGDVNGHKFSVSGEGEGDATYGKITAKAICTTGKLPVPWPTLSTVFSYGNRCFSRYPDHMKQHDFFKSAMPEGYVWERTIFFKDDGNYKTRAEIKFEGDTLVSRIELKGIDFKEDGNILGHKLEYNLPSTNKYIMADKQKNGIKVNAKIRHNIEDGSVQLADHYQQNTPIGDGPVLLPDNHYLSEQLALSKDPNEKRDHMVVLEFVTAAGITLGMDELYK</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>ATGGTGAGCAAAGGCGAAGAACTGTTTACCGGCGTGGTGCCGATTCTGGTGGAACTGGATGGCGATGTGAACGGCCATAAATTTAGCGTGAGCGGCGAAGGCGAAGGCGATGCGACCTATGGCAAAATTACCGCGAAAGCGATTTGCACCACCGGCAAACTGCCGGTGCCGTGGCCGACCCTGAGCACCGTGTTTAGCTATGGCAACCGCTGCTTTAGCCGCTATCCGGATCATATGAAACAGCATGATTTTTTTAAAAGCGCGATGCCGGAAGGCTATGTGTGGGAACGCACCATTTTTTTTAAAGATGATGGCAACTATAAAACCCGCGCGGAAATTAAATTTGAAGGCGATACCCTGGTGAGCCGCATTGAACTGAAAGGCATTGATTTTAAAGAAGATGGCAACATTCTGGGCCATAAACTGGAATATAACCTGCCGAGCACCAACAAATATATTATGGCGGATAAACAGAAAAACGGCATTAAAGTGAACGCGAAAATTCGCCATAACATTGAAGATGGCAGCGTGCAGCTGGCGGATCATTATCAGCAGAACACCCCGATTGGCGATGGCCCGGTGCTGCTGCCGGATAACCATTATCTGAGCGAACAGCTGGCGCTGAGCAAAGATCCGAACGAAAAACGCGATCATATGGTGGTGCTGGAATTTGTGACCGCGGCGGGCATTACCCTGGGCATGGATGAACTGTATAAATAA</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>